--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peril Conversions" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protection Class Conversions" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Building Codes By State" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Codes" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1698,6 +1699,106 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClassCodeMin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Program</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Hab</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>70000</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>80000</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1792,7 +1893,6 @@
           <t>FooterRightTemplate</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1805,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3546,6 +3646,740 @@
       </c>
       <c r="D104" t="n">
         <v>70</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>TR_AP</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>TR_AP</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>2</v>
+      </c>
+      <c r="C106" t="n">
+        <v>5</v>
+      </c>
+      <c r="D106" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>PCBG_AP</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>PCBG_AP</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>2</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>PCPP_AP</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>PCPP_AP</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>2</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>MVBG_AP</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>MVBG_AP</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>2</v>
+      </c>
+      <c r="C112" t="n">
+        <v>2</v>
+      </c>
+      <c r="D112" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>MVPP_AP</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>MVPP_AP</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>2</v>
+      </c>
+      <c r="C114" t="n">
+        <v>2</v>
+      </c>
+      <c r="D114" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>PD_AP</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="n">
+        <v>3</v>
+      </c>
+      <c r="D115" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>PD_AP</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>4</v>
+      </c>
+      <c r="C116" t="n">
+        <v>4</v>
+      </c>
+      <c r="D116" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>PD_AP</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>5</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>WHBBG_AP</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>WHBBG_AP</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>2</v>
+      </c>
+      <c r="C119" t="n">
+        <v>2</v>
+      </c>
+      <c r="D119" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>WHBBG_AP</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>3</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>WHBPP_AP</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>WHBPP_AP</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>2</v>
+      </c>
+      <c r="C122" t="n">
+        <v>2</v>
+      </c>
+      <c r="D122" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>WHBPP_AP</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>3</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>WHPBG_AP</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>WHPBG_AP</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>2</v>
+      </c>
+      <c r="C125" t="n">
+        <v>2</v>
+      </c>
+      <c r="D125" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>WHPBG_AP</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>3</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>WHPPP_AP</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>WHPPP_AP</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>2</v>
+      </c>
+      <c r="C128" t="n">
+        <v>2</v>
+      </c>
+      <c r="D128" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>WHPPP_AP</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>3</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>CSFA_AP</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>BABG_AP</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>BABG_AP</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>2</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>BAPP_AP</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>BAPP_AP</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>2</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>BABI_AP</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>BABI_AP</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>2</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>AIBG_AP</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" t="n">
+        <v>2</v>
+      </c>
+      <c r="D137" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>AIBG_AP</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>3</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>AIPP_AP</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" t="n">
+        <v>2</v>
+      </c>
+      <c r="D139" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>AIPP_AP</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>3</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>BCEG_AP_SINGLE</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>BCEG_AP_SINGLE</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>2</v>
+      </c>
+      <c r="C142" t="n">
+        <v>2</v>
+      </c>
+      <c r="D142" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>TIB_AP</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>TIB_AP</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>2</v>
+      </c>
+      <c r="C144" t="n">
+        <v>2</v>
+      </c>
+      <c r="D144" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>WHPBG_AP_CURRENT</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>WHPBG_AP_CURRENT</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>2</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>WHPPP_AP_CURRENT</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>WHPPP_AP_CURRENT</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>2</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -3559,7 +4393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4016,6 +4850,216 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PD_AP</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WHBBG_AP</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WHBPP_AP</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WHPBG_AP</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WHPPP_AP</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BABG_AP</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NoDecimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BAPP_AP</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NoDecimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BABI_AP</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NoDecimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AIBG_AP</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NoDecimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AIPP_AP</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NoDecimal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4027,7 +5071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4105,7 +5149,6 @@
           <t>E:REST</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4136,7 +5179,6 @@
           <t>E:REST</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4307,7 +5349,6 @@
           <t>C:REST</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4338,7 +5379,6 @@
           <t>C:REST</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4364,8 +5404,6 @@
           <t>Entire State</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4391,8 +5429,6 @@
           <t>Total Property Limit</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4463,6 +5499,126 @@
           <t>Wind-Hail Deductible</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PD_AP</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>B:D</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Amount of Insurance</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>E:REST</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AIBG_AP</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A:B</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Building Limit</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>C:REST</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AIPP_AP</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A:B</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Building Limit</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>C:REST</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BCEG_AP_SINGLE</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>B:REST</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Entire State</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D148"/>
+  <dimension ref="A1:D189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4380,6 +4380,682 @@
       </c>
       <c r="D148" t="n">
         <v>80</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>HAB_BR</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>HAB_BR</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>2</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>HAB_LA</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>AS_BR</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>AS_BR</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>2</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>PROGRAM_TR</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>PROGRAM_TR</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>2</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>CBG</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>CBG</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>2</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>2</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>YBBG</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>YBBG</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>2</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>YBPP</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>YBPP</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>2</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>PDLD</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>PDLD</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>2</v>
+      </c>
+      <c r="C166" t="n">
+        <v>2</v>
+      </c>
+      <c r="D166" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>1</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>2</v>
+      </c>
+      <c r="C168" t="n">
+        <v>2</v>
+      </c>
+      <c r="D168" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>4</v>
+      </c>
+      <c r="C170" t="n">
+        <v>4</v>
+      </c>
+      <c r="D170" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>DONM</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>1</v>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>2</v>
+      </c>
+      <c r="C172" t="n">
+        <v>2</v>
+      </c>
+      <c r="D172" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>PLUS</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>1</v>
+      </c>
+      <c r="C173" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>1</v>
+      </c>
+      <c r="C174" t="n">
+        <v>1</v>
+      </c>
+      <c r="D174" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>2</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>CW</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>1</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>CW</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>2</v>
+      </c>
+      <c r="C177" t="n">
+        <v>2</v>
+      </c>
+      <c r="D177" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>1</v>
+      </c>
+      <c r="C178" t="n">
+        <v>2</v>
+      </c>
+      <c r="D178" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>3</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>LS_CURRENT</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>1</v>
+      </c>
+      <c r="C180" t="n">
+        <v>2</v>
+      </c>
+      <c r="D180" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>LS_CURRENT</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>3</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>LPGE</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>LPGE</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>2</v>
+      </c>
+      <c r="C183" t="n">
+        <v>2</v>
+      </c>
+      <c r="D183" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>AIGO</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>1</v>
+      </c>
+      <c r="C184" t="n">
+        <v>1</v>
+      </c>
+      <c r="D184" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>BGL</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>1</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1</v>
+      </c>
+      <c r="D185" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>SPD</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>1</v>
+      </c>
+      <c r="C186" t="n">
+        <v>1</v>
+      </c>
+      <c r="D186" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>SPD</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>2</v>
+      </c>
+      <c r="C187" t="n">
+        <v>2</v>
+      </c>
+      <c r="D187" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>1</v>
+      </c>
+      <c r="C188" t="n">
+        <v>1</v>
+      </c>
+      <c r="D188" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>2</v>
+      </c>
+      <c r="C189" t="n">
+        <v>2</v>
+      </c>
+      <c r="D189" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -4393,7 +5069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5060,6 +5736,409 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>HAB_BR</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>#,##0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>HAB_LA</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>#,##0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AS_BR</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>#,##0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>YBBG</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>###0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>YBPP</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>###0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>EBB</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>$#,##0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PDLD</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>NoDecimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>NoDecimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NoDecimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>3</v>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>$#,##0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DONM</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NoDecimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DONM</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>$#,##0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PLUS</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>$#,##0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>NoDecimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>LS_CURRENT</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>NoDecimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>LPGE</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>NoDecimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>LPGE</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SPD</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>$#,##0.00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5071,7 +6150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5529,7 +6608,6 @@
           <t>E:REST</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5560,7 +6638,6 @@
           <t>C:REST</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5591,7 +6668,6 @@
           <t>C:REST</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5617,8 +6693,68 @@
           <t>Entire State</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A:B</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Receipts Range</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>C:REST</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LS_CURRENT</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>A:B</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Receipts Range</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>C:REST</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>$#,##0</t>
+          <t>$#,##0.000</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>#,##0</t>
+          <t>#,##0.000</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>#,##0.0000</t>
+          <t>#,##0.000</t>
         </is>
       </c>
     </row>
@@ -5799,7 +5799,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>#,##0.0000</t>
+          <t>#,##0.000</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>###0</t>
+          <t>#,##0.000</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>###0</t>
+          <t>#,##0.000</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>$#,##0.00</t>
+          <t>$#,##0.000</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>$#,##0.00</t>
+          <t>$#,##0.000</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>$#,##0.00</t>
+          <t>$#,##0.000</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>$#,##0.00</t>
+          <t>$#,##0.000</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$#,##0.00</t>
+          <t>$#,##0.000</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6723,6 @@
           <t>C:REST</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6754,7 +6753,6 @@
           <t>C:REST</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -1845,7 +1845,7 @@
       <c r="B3" t="inlineStr">
         <is>
           <t xml:space="preserve">
-{state} - Rate Pages</t>
+{state} - {program}</t>
         </is>
       </c>
     </row>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -1832,7 +1832,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Commercial Lines Manual: Division Nine - Businessowners</t>
+          <t>Commercial Lines Manual - Businessowners</t>
         </is>
       </c>
     </row>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D189"/>
+  <dimension ref="A1:D205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5056,6 +5056,270 @@
       </c>
       <c r="D189" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>NSPP</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>1</v>
+      </c>
+      <c r="C190" t="n">
+        <v>2</v>
+      </c>
+      <c r="D190" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>NSPP</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>3</v>
+      </c>
+      <c r="C191" t="n">
+        <v>3</v>
+      </c>
+      <c r="D191" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>NSPP</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>4</v>
+      </c>
+      <c r="C192" t="n">
+        <v>4</v>
+      </c>
+      <c r="D192" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>NSPP</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>5</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>NSPPH</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>1</v>
+      </c>
+      <c r="C194" t="n">
+        <v>2</v>
+      </c>
+      <c r="D194" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>NSPPH</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>3</v>
+      </c>
+      <c r="C195" t="n">
+        <v>3</v>
+      </c>
+      <c r="D195" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>NSPPH</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>4</v>
+      </c>
+      <c r="C196" t="n">
+        <v>4</v>
+      </c>
+      <c r="D196" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>NSPPH</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>5</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>NSBG</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1</v>
+      </c>
+      <c r="C198" t="n">
+        <v>2</v>
+      </c>
+      <c r="D198" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>NSBG</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>3</v>
+      </c>
+      <c r="C199" t="n">
+        <v>3</v>
+      </c>
+      <c r="D199" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>NSBG</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>4</v>
+      </c>
+      <c r="C200" t="n">
+        <v>4</v>
+      </c>
+      <c r="D200" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>NSBG</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>5</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>NSBGH</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" t="n">
+        <v>2</v>
+      </c>
+      <c r="D202" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>NSBGH</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>3</v>
+      </c>
+      <c r="C203" t="n">
+        <v>3</v>
+      </c>
+      <c r="D203" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>NSBGH</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>4</v>
+      </c>
+      <c r="C204" t="n">
+        <v>4</v>
+      </c>
+      <c r="D204" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>NSBGH</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>5</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -5069,7 +5333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6139,6 +6403,90 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>NSPP</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>NSPPH</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" t="n">
+        <v>5</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>NSBG</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>4</v>
+      </c>
+      <c r="D53" t="n">
+        <v>5</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>NSBGH</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" t="n">
+        <v>5</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6150,7 +6498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6751,6 +7099,146 @@
       <c r="F19" t="inlineStr">
         <is>
           <t>C:REST</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NSPP</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>B:D</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Amount of Insurance</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>E:REST</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Named Storm Deductible</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NSPPH</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>B:D</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Amount of Insurance</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>E:REST</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Named Storm Deductible</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NSBG</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>B:D</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Amount of Insurance</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>E:REST</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Named Storm Deductible</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NSBGH</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>B:D</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Amount of Insurance</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>E:REST</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Named Storm Deductible</t>
         </is>
       </c>
     </row>
@@ -6818,7 +7306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6852,10 +7340,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>NSPP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fit_width_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NSBG</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fit_width_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>*</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>fit_single_page</t>
         </is>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -6420,7 +6420,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D205"/>
+  <dimension ref="A1:D217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5320,6 +5320,206 @@
       </c>
       <c r="D205" t="n">
         <v>62</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>NSPPP</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>1</v>
+      </c>
+      <c r="C206" t="n">
+        <v>1</v>
+      </c>
+      <c r="D206" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>NSPPP</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>2</v>
+      </c>
+      <c r="C207" t="n">
+        <v>2</v>
+      </c>
+      <c r="D207" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>NSPPP</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>3</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>NSPPPH</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>1</v>
+      </c>
+      <c r="C209" t="n">
+        <v>1</v>
+      </c>
+      <c r="D209" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>NSPPPH</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>2</v>
+      </c>
+      <c r="C210" t="n">
+        <v>2</v>
+      </c>
+      <c r="D210" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>NSPPPH</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>3</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>NSPBG</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1</v>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+      <c r="D212" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>NSPBG</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>2</v>
+      </c>
+      <c r="C213" t="n">
+        <v>2</v>
+      </c>
+      <c r="D213" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>NSPBG</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>3</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>NSPBGH</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>1</v>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+      <c r="D215" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>NSPBGH</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>2</v>
+      </c>
+      <c r="C216" t="n">
+        <v>2</v>
+      </c>
+      <c r="D216" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>NSPBGH</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>3</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D217"/>
+  <dimension ref="A1:D223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5520,6 +5520,106 @@
       </c>
       <c r="D217" t="n">
         <v>70</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>NSPPP_AP</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>1</v>
+      </c>
+      <c r="C218" t="n">
+        <v>1</v>
+      </c>
+      <c r="D218" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>NSPPP_AP</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>2</v>
+      </c>
+      <c r="C219" t="n">
+        <v>2</v>
+      </c>
+      <c r="D219" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>NSPPP_AP</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>3</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>NSPBG_AP</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>1</v>
+      </c>
+      <c r="C221" t="n">
+        <v>1</v>
+      </c>
+      <c r="D221" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>NSPBG_AP</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>2</v>
+      </c>
+      <c r="C222" t="n">
+        <v>2</v>
+      </c>
+      <c r="D222" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>NSPBG_AP</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>3</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -1883,7 +1883,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">{state_abb} - &amp;[Tab] - &amp;P </t>
+          <t xml:space="preserve">{section} - {state_abb} - &amp;[Tab] - &amp;P </t>
         </is>
       </c>
     </row>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -5633,7 +5633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6782,6 +6782,132 @@
         <v>5</v>
       </c>
       <c r="E54" t="inlineStr">
+        <is>
+          <t>$#,##0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>NSPPP</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>$#,##0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>NSPPPH</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>$#,##0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NSPBG</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>$#,##0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>NSPBGH</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>$#,##0</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>NSPPP_AP</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="n">
+        <v>4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>$#,##0</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>NSPBG_AP</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" t="n">
+        <v>4</v>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>$#,##0</t>
         </is>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -7732,7 +7732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7790,10 +7790,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>PDLD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fit_single_page</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fit_width_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>*</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>fit_single_page</t>
         </is>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -7807,7 +7807,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fit_width_only</t>
+          <t>disable_fit_to_page</t>
         </is>
       </c>
     </row>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -5687,7 +5687,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:D220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2225,69 +2225,71 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D19" t="n">
-        <v>74</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>PDH</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
-      </c>
-      <c r="C20" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D20" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>WHOBG</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PDH</t>
+          <t>WHOBG</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PDH</t>
+          <t>WHOBG</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2303,7 +2305,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PDH</t>
+          <t>WHOBG</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2315,13 +2317,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WHOBG</t>
+          <t>WHOBGH</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2337,7 +2339,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WHOBG</t>
+          <t>WHOBGH</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2353,7 +2355,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WHOBG</t>
+          <t>WHOBGH</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2369,7 +2371,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WHOBG</t>
+          <t>WHOBGH</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2387,7 +2389,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WHOBGH</t>
+          <t>WHOPP</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2403,7 +2405,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WHOBGH</t>
+          <t>WHOPP</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2419,7 +2421,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>WHOBGH</t>
+          <t>WHOPP</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2435,7 +2437,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>WHOBGH</t>
+          <t>WHOPP</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2453,7 +2455,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>WHOPP</t>
+          <t>WHOPPH</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2469,7 +2471,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>WHOPP</t>
+          <t>WHOPPH</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2485,7 +2487,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>WHOPP</t>
+          <t>WHOPPH</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2501,7 +2503,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>WHOPP</t>
+          <t>WHOPPH</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2519,459 +2521,459 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>WHOPPH</t>
+          <t>WHBBG</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>74</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>WHOPPH</t>
+          <t>WHBBG</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>105</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WHOPPH</t>
+          <t>WHBBG</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
-      </c>
-      <c r="C39" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D39" t="n">
-        <v>105</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>WHOPPH</t>
+          <t>WHBBGH</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>62</v>
+        <v>222</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>WHBBG</t>
+          <t>WHBBGH</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>222</v>
+        <v>159</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>WHBBG</t>
+          <t>WHBBGH</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
-      </c>
-      <c r="C42" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D42" t="n">
-        <v>159</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>WHBBG</t>
+          <t>WHBPP</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>70</v>
+        <v>222</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>WHBBGH</t>
+          <t>WHBPP</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>222</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>WHBBGH</t>
+          <t>WHBPP</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
-      </c>
-      <c r="C45" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D45" t="n">
-        <v>159</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>WHBBGH</t>
+          <t>WHBPPH</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>70</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WHBPP</t>
+          <t>WHBPPH</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>222</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>WHBPP</t>
+          <t>WHBPPH</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
-      </c>
-      <c r="C48" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D48" t="n">
-        <v>159</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>WHBPP</t>
+          <t>WHPBG</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>70</v>
+        <v>159</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>WHBPPH</t>
+          <t>WHPBG</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>222</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>WHBPPH</t>
+          <t>WHPBG</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
-      </c>
-      <c r="C51" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D51" t="n">
-        <v>159</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>WHBPPH</t>
+          <t>WHPBGH</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>70</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>WHPBG</t>
+          <t>WHPBGH</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>159</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>WHPBG</t>
+          <t>WHPBGH</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
-      </c>
-      <c r="C54" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D54" t="n">
-        <v>105</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WHPBG</t>
+          <t>WHPPP</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>70</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>WHPBGH</t>
+          <t>WHPPP</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>159</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>WHPBGH</t>
+          <t>WHPPP</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
-      </c>
-      <c r="C57" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D57" t="n">
-        <v>105</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>WHPBGH</t>
+          <t>WHPPPH</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>70</v>
+        <v>159</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>WHPPP</t>
+          <t>WHPPPH</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>159</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>WHPPP</t>
+          <t>WHPPPH</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
-      </c>
-      <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D60" t="n">
-        <v>105</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>WHPPP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>WHPPPH</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>WHPPPH</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WHPPPH</t>
+          <t>CSFA</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2979,13 +2981,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>BABG</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -2995,49 +2997,51 @@
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>82</v>
+        <v>145</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>BABG</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>2</v>
       </c>
-      <c r="C66" t="n">
-        <v>2</v>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D66" t="n">
-        <v>166</v>
+        <v>53</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>BAPP</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>96</v>
+        <v>145</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CSFA</t>
+          <t>BAPP</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3045,13 +3049,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>91</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BABG</t>
+          <t>BABI</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3067,7 +3071,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BABG</t>
+          <t>BABI</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -3085,27 +3089,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BAPP</t>
+          <t>AIBG</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>145</v>
+        <v>82</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BAPP</t>
+          <t>AIBG</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3119,27 +3123,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BABI</t>
+          <t>AIPP</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>145</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BABI</t>
+          <t>AIPP</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3153,48 +3157,46 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AIBG</t>
+          <t>BCEG_MULTI</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AIBG</t>
+          <t>BCEG_MULTI</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C76" t="n">
+        <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AIPP</t>
+          <t>BCEG_MULTI</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D77" t="n">
         <v>82</v>
@@ -3203,11 +3205,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AIPP</t>
+          <t>BCEG_MULTI</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3221,7 +3223,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCEG_MULTI</t>
+          <t>BCEG_SINGLE</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3231,36 +3233,38 @@
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCEG_MULTI</t>
+          <t>BCEG_SINGLE</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>2</v>
       </c>
-      <c r="C80" t="n">
-        <v>2</v>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D80" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCEG_MULTI</t>
+          <t>TIB</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
         <v>82</v>
@@ -3269,109 +3273,105 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCEG_MULTI</t>
+          <t>TIB</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C82" t="n">
+        <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCEG_SINGLE</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>1</v>
       </c>
-      <c r="C83" t="n">
-        <v>1</v>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D83" t="n">
-        <v>82</v>
+        <v>180</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCEG_SINGLE</t>
+          <t>EBD</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>53</v>
+        <v>145</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TIB</t>
+          <t>EBD</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TIB</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>68</v>
+        <v>180</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C87" t="n">
+        <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>180</v>
+        <v>68</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EBD</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -3381,13 +3381,13 @@
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>145</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EBD</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -3397,179 +3397,183 @@
         <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>68</v>
+        <v>150</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D90" t="n">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WHOBG_CURRENT</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>WHOBG_CURRENT</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>WHOBG_CURRENT</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2</v>
-      </c>
-      <c r="C93" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D93" t="n">
-        <v>150</v>
+        <v>62</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>WHOPP_CURRENT</t>
         </is>
       </c>
       <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="n">
         <v>3</v>
       </c>
-      <c r="C94" t="n">
-        <v>6</v>
-      </c>
       <c r="D94" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>WHOBG_CURRENT</t>
+          <t>WHOPP_CURRENT</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D95" t="n">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>WHOBG_CURRENT</t>
+          <t>WHOPP_CURRENT</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4</v>
-      </c>
-      <c r="C96" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D96" t="n">
-        <v>105</v>
+        <v>62</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>WHOBG_CURRENT</t>
+          <t>WHPBG_CURRENT</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>5</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>62</v>
+        <v>159</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>WHOPP_CURRENT</t>
+          <t>WHPBG_CURRENT</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
-      </c>
-      <c r="C98" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D98" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>WHOPP_CURRENT</t>
+          <t>WHPPP_CURRENT</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>105</v>
+        <v>159</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>WHOPP_CURRENT</t>
+          <t>WHPPP_CURRENT</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -3577,13 +3581,13 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>WHPBG_CURRENT</t>
+          <t>TR_AP</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -3593,31 +3597,29 @@
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>WHPBG_CURRENT</t>
+          <t>TR_AP</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>2</v>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+      <c r="C102" t="n">
+        <v>5</v>
       </c>
       <c r="D102" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>WHPPP_CURRENT</t>
+          <t>PCBG_AP</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -3627,13 +3629,13 @@
         <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>159</v>
+        <v>131</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>WHPPP_CURRENT</t>
+          <t>PCBG_AP</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -3645,13 +3647,13 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TR_AP</t>
+          <t>PCPP_AP</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -3661,20 +3663,22 @@
         <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>150</v>
+        <v>131</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TR_AP</t>
+          <t>PCPP_AP</t>
         </is>
       </c>
       <c r="B106" t="n">
         <v>2</v>
       </c>
-      <c r="C106" t="n">
-        <v>5</v>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D106" t="n">
         <v>80</v>
@@ -3683,7 +3687,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PCBG_AP</t>
+          <t>MVBG_AP</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -3693,31 +3697,29 @@
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>131</v>
+        <v>215</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PCBG_AP</t>
+          <t>MVBG_AP</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>2</v>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+      <c r="C108" t="n">
+        <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PCPP_AP</t>
+          <t>MVPP_AP</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -3727,131 +3729,133 @@
         <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>131</v>
+        <v>215</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PCPP_AP</t>
+          <t>MVPP_AP</t>
         </is>
       </c>
       <c r="B110" t="n">
         <v>2</v>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+      <c r="C110" t="n">
+        <v>2</v>
       </c>
       <c r="D110" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MVBG_AP</t>
+          <t>PD_AP</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1</v>
-      </c>
-      <c r="C111" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D111" t="n">
-        <v>215</v>
+        <v>80</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MVBG_AP</t>
+          <t>WHBBG_AP</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>100</v>
+        <v>222</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MVPP_AP</t>
+          <t>WHBBG_AP</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113" t="n">
-        <v>215</v>
+        <v>150</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MVPP_AP</t>
+          <t>WHBBG_AP</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2</v>
-      </c>
-      <c r="C114" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D114" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>PD_AP</t>
+          <t>WHBPP_AP</t>
         </is>
       </c>
       <c r="B115" t="n">
         <v>1</v>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>74</v>
+        <v>222</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PD_AP</t>
+          <t>WHBPP_AP</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C116" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D116" t="n">
-        <v>105</v>
+        <v>150</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PD_AP</t>
+          <t>WHBPP_AP</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -3865,7 +3869,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>WHBBG_AP</t>
+          <t>WHPBG_AP</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -3875,13 +3879,13 @@
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>222</v>
+        <v>159</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>WHBBG_AP</t>
+          <t>WHPBG_AP</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -3891,13 +3895,13 @@
         <v>2</v>
       </c>
       <c r="D119" t="n">
-        <v>150</v>
+        <v>105</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>WHBBG_AP</t>
+          <t>WHPBG_AP</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -3915,7 +3919,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>WHBPP_AP</t>
+          <t>WHPPP_AP</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -3925,13 +3929,13 @@
         <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>222</v>
+        <v>159</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>WHBPP_AP</t>
+          <t>WHPPP_AP</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -3941,13 +3945,13 @@
         <v>2</v>
       </c>
       <c r="D122" t="n">
-        <v>150</v>
+        <v>105</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>WHBPP_AP</t>
+          <t>WHPPP_AP</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -3965,43 +3969,45 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>WHPBG_AP</t>
+          <t>CSFA_AP</t>
         </is>
       </c>
       <c r="B124" t="n">
         <v>1</v>
       </c>
-      <c r="C124" t="n">
-        <v>1</v>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D124" t="n">
-        <v>159</v>
+        <v>100</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>WHPBG_AP</t>
+          <t>BABG_AP</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>105</v>
+        <v>145</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>WHPBG_AP</t>
+          <t>BABG_AP</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -4015,7 +4021,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>WHPPP_AP</t>
+          <t>BAPP_AP</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -4025,51 +4031,51 @@
         <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>159</v>
+        <v>145</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>WHPPP_AP</t>
+          <t>BAPP_AP</t>
         </is>
       </c>
       <c r="B128" t="n">
         <v>2</v>
       </c>
-      <c r="C128" t="n">
-        <v>2</v>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D128" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>WHPPP_AP</t>
+          <t>BABI_AP</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>3</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>80</v>
+        <v>145</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CSFA_AP</t>
+          <t>BABI_AP</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -4077,33 +4083,33 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BABG_AP</t>
+          <t>AIBG_AP</t>
         </is>
       </c>
       <c r="B131" t="n">
         <v>1</v>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D131" t="n">
-        <v>145</v>
+        <v>82</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BABG_AP</t>
+          <t>AIBG_AP</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -4117,27 +4123,27 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BAPP_AP</t>
+          <t>AIPP_AP</t>
         </is>
       </c>
       <c r="B133" t="n">
         <v>1</v>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D133" t="n">
-        <v>145</v>
+        <v>82</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BAPP_AP</t>
+          <t>AIPP_AP</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -4151,7 +4157,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BABI_AP</t>
+          <t>BCEG_AP_SINGLE</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -4161,85 +4167,81 @@
         <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>145</v>
+        <v>82</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BABI_AP</t>
+          <t>BCEG_AP_SINGLE</t>
         </is>
       </c>
       <c r="B136" t="n">
         <v>2</v>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+      <c r="C136" t="n">
+        <v>2</v>
       </c>
       <c r="D136" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AIBG_AP</t>
+          <t>TIB_AP</t>
         </is>
       </c>
       <c r="B137" t="n">
         <v>1</v>
       </c>
       <c r="C137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AIBG_AP</t>
+          <t>TIB_AP</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>3</v>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C138" t="n">
+        <v>2</v>
       </c>
       <c r="D138" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AIPP_AP</t>
+          <t>WHPBG_AP_CURRENT</t>
         </is>
       </c>
       <c r="B139" t="n">
         <v>1</v>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>82</v>
+        <v>159</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>AIPP_AP</t>
+          <t>WHPBG_AP_CURRENT</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -4253,7 +4255,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BCEG_AP_SINGLE</t>
+          <t>WHPPP_AP_CURRENT</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -4263,29 +4265,31 @@
         <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>82</v>
+        <v>159</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BCEG_AP_SINGLE</t>
+          <t>WHPPP_AP_CURRENT</t>
         </is>
       </c>
       <c r="B142" t="n">
         <v>2</v>
       </c>
-      <c r="C142" t="n">
-        <v>2</v>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D142" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TIB_AP</t>
+          <t>HAB_BR</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -4295,29 +4299,31 @@
         <v>1</v>
       </c>
       <c r="D143" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TIB_AP</t>
+          <t>HAB_BR</t>
         </is>
       </c>
       <c r="B144" t="n">
         <v>2</v>
       </c>
-      <c r="C144" t="n">
-        <v>2</v>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D144" t="n">
-        <v>68</v>
+        <v>120</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>WHPBG_AP_CURRENT</t>
+          <t>HAB_LA</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -4327,38 +4333,38 @@
         <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>WHPBG_AP_CURRENT</t>
+          <t>AS_BR</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>2</v>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
       </c>
       <c r="D146" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>WHPPP_AP_CURRENT</t>
+          <t>AS_BR</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1</v>
-      </c>
-      <c r="C147" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D147" t="n">
         <v>159</v>
@@ -4367,75 +4373,75 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>WHPPP_AP_CURRENT</t>
+          <t>PROGRAM_TR</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>HAB_BR</t>
+          <t>PROGRAM_TR</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1</v>
-      </c>
-      <c r="C149" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D149" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>HAB_BR</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>2</v>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
       </c>
       <c r="D150" t="n">
-        <v>120</v>
+        <v>138</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>HAB_LA</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1</v>
-      </c>
-      <c r="C151" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D151" t="n">
-        <v>150</v>
+        <v>53</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>AS_BR</t>
+          <t>CPP</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -4445,13 +4451,13 @@
         <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>82</v>
+        <v>138</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>AS_BR</t>
+          <t>CPP</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -4463,13 +4469,13 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>159</v>
+        <v>53</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PROGRAM_TR</t>
+          <t>YBBG</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -4479,13 +4485,13 @@
         <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>70</v>
+        <v>131</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PROGRAM_TR</t>
+          <t>YBBG</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -4497,13 +4503,13 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>YBPP</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -4513,13 +4519,13 @@
         <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>YBPP</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -4537,7 +4543,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CPP</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -4547,115 +4553,109 @@
         <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CPP</t>
+          <t>PDLD</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>2</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>53</v>
+        <v>187</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>YBBG</t>
+          <t>PDLD</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D160" t="n">
-        <v>131</v>
+        <v>54</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>YBBG</t>
+          <t>LL</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>2</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C161" t="n">
+        <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>53</v>
+        <v>205</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>YBPP</t>
+          <t>LL</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D162" t="n">
-        <v>131</v>
+        <v>54</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>YBPP</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>2</v>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>53</v>
+        <v>130</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D164" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PDLD</t>
+          <t>DONM</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -4665,13 +4665,13 @@
         <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>187</v>
+        <v>225</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PDLD</t>
+          <t>ERP</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -4681,13 +4681,13 @@
         <v>2</v>
       </c>
       <c r="D166" t="n">
-        <v>54</v>
+        <v>215</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>LL</t>
+          <t>PLUS</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -4697,129 +4697,133 @@
         <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>205</v>
+        <v>350</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>LL</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1</v>
-      </c>
-      <c r="C169" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D169" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>CW</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C170" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>140</v>
+        <v>124</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>DONM</t>
+          <t>CW</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D171" t="n">
-        <v>225</v>
+        <v>54</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ERP</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C172" t="n">
         <v>2</v>
       </c>
       <c r="D172" t="n">
-        <v>215</v>
+        <v>95</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>1</v>
-      </c>
-      <c r="C173" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D173" t="n">
-        <v>350</v>
+        <v>120</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>LS_CURRENT</t>
         </is>
       </c>
       <c r="B174" t="n">
         <v>1</v>
       </c>
       <c r="C174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D174" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>LS_CURRENT</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -4827,13 +4831,13 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>80</v>
+        <v>195</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CW</t>
+          <t>LPGE</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -4843,13 +4847,13 @@
         <v>1</v>
       </c>
       <c r="D176" t="n">
-        <v>124</v>
+        <v>205</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CW</t>
+          <t>LPGE</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -4859,81 +4863,77 @@
         <v>2</v>
       </c>
       <c r="D177" t="n">
-        <v>54</v>
+        <v>200</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>AIGO</t>
         </is>
       </c>
       <c r="B178" t="n">
         <v>1</v>
       </c>
       <c r="C178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>95</v>
+        <v>480</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>BGL</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>3</v>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C179" t="n">
+        <v>1</v>
       </c>
       <c r="D179" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>LS_CURRENT</t>
+          <t>SPD</t>
         </is>
       </c>
       <c r="B180" t="n">
         <v>1</v>
       </c>
       <c r="C180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D180" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>LS_CURRENT</t>
+          <t>SPD</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>3</v>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C181" t="n">
+        <v>2</v>
       </c>
       <c r="D181" t="n">
-        <v>195</v>
+        <v>54</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>LPGE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -4943,13 +4943,13 @@
         <v>1</v>
       </c>
       <c r="D182" t="n">
-        <v>205</v>
+        <v>145</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>LPGE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -4959,346 +4959,350 @@
         <v>2</v>
       </c>
       <c r="D183" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>AIGO</t>
+          <t>NSPP</t>
         </is>
       </c>
       <c r="B184" t="n">
         <v>1</v>
       </c>
       <c r="C184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D184" t="n">
-        <v>480</v>
+        <v>74</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>BGL</t>
+          <t>NSPP</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D185" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SPD</t>
+          <t>NSPP</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C186" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D186" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SPD</t>
+          <t>NSPP</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>2</v>
-      </c>
-      <c r="C187" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D187" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>NSPPH</t>
         </is>
       </c>
       <c r="B188" t="n">
         <v>1</v>
       </c>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D188" t="n">
-        <v>145</v>
+        <v>74</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>NSPPH</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D189" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>NSPP</t>
+          <t>NSPPH</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C190" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D190" t="n">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>NSPP</t>
+          <t>NSPPH</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>3</v>
-      </c>
-      <c r="C191" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D191" t="n">
-        <v>105</v>
+        <v>62</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>NSPP</t>
+          <t>NSBG</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C192" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D192" t="n">
-        <v>105</v>
+        <v>74</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>NSPP</t>
+          <t>NSBG</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>5</v>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C193" t="n">
+        <v>3</v>
       </c>
       <c r="D193" t="n">
-        <v>62</v>
+        <v>105</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>NSPPH</t>
+          <t>NSBG</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C194" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D194" t="n">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>NSPPH</t>
+          <t>NSBG</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>3</v>
-      </c>
-      <c r="C195" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D195" t="n">
-        <v>105</v>
+        <v>62</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>NSPPH</t>
+          <t>NSBGH</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C196" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D196" t="n">
-        <v>105</v>
+        <v>74</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>NSPPH</t>
+          <t>NSBGH</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>5</v>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C197" t="n">
+        <v>3</v>
       </c>
       <c r="D197" t="n">
-        <v>62</v>
+        <v>105</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>NSBG</t>
+          <t>NSBGH</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C198" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D198" t="n">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>NSBG</t>
+          <t>NSBGH</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>3</v>
-      </c>
-      <c r="C199" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D199" t="n">
-        <v>105</v>
+        <v>62</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>NSBG</t>
+          <t>NSPPP</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C200" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D200" t="n">
-        <v>105</v>
+        <v>159</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>NSBG</t>
+          <t>NSPPP</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>5</v>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C201" t="n">
+        <v>2</v>
       </c>
       <c r="D201" t="n">
-        <v>62</v>
+        <v>105</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>NSBGH</t>
+          <t>NSPPP</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>1</v>
-      </c>
-      <c r="C202" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
       </c>
       <c r="D202" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>NSBGH</t>
+          <t>NSPPPH</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C203" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D203" t="n">
-        <v>105</v>
+        <v>159</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>NSBGH</t>
+          <t>NSPPPH</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C204" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D204" t="n">
         <v>105</v>
@@ -5307,11 +5311,11 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>NSBGH</t>
+          <t>NSPPPH</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -5319,13 +5323,13 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>NSPPP</t>
+          <t>NSPBG</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -5341,7 +5345,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>NSPPP</t>
+          <t>NSPBG</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -5357,7 +5361,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>NSPPP</t>
+          <t>NSPBG</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -5375,7 +5379,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>NSPPPH</t>
+          <t>NSPBGH</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -5391,7 +5395,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>NSPPPH</t>
+          <t>NSPBGH</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -5407,7 +5411,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>NSPPPH</t>
+          <t>NSPBGH</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -5425,7 +5429,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>NSPBG</t>
+          <t>NSPPP_AP</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -5441,7 +5445,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>NSPBG</t>
+          <t>NSPPP_AP</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -5457,7 +5461,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>NSPBG</t>
+          <t>NSPPP_AP</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -5469,13 +5473,13 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>NSPBGH</t>
+          <t>NSPBG_AP</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -5491,7 +5495,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>NSPBGH</t>
+          <t>NSPBG_AP</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -5507,7 +5511,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>NSPBGH</t>
+          <t>NSPBG_AP</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -5519,36 +5523,36 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>NSPPP_AP</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="B218" t="n">
         <v>1</v>
       </c>
       <c r="C218" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D218" t="n">
-        <v>159</v>
+        <v>105</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>NSPPP_AP</t>
+          <t>PDH</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C219" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D219" t="n">
         <v>105</v>
@@ -5557,69 +5561,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>NSPPP_AP</t>
+          <t>PD_AP</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>3</v>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C220" t="n">
+        <v>4</v>
       </c>
       <c r="D220" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>NSPBG_AP</t>
-        </is>
-      </c>
-      <c r="B221" t="n">
-        <v>1</v>
-      </c>
-      <c r="C221" t="n">
-        <v>1</v>
-      </c>
-      <c r="D221" t="n">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>NSPBG_AP</t>
-        </is>
-      </c>
-      <c r="B222" t="n">
-        <v>2</v>
-      </c>
-      <c r="C222" t="n">
-        <v>2</v>
-      </c>
-      <c r="D222" t="n">
         <v>105</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>NSPBG_AP</t>
-        </is>
-      </c>
-      <c r="B223" t="n">
-        <v>3</v>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -7807,7 +7759,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>disable_fit_to_page</t>
+          <t>fit_width_landscape</t>
         </is>
       </c>
     </row>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -7684,7 +7684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7766,10 +7766,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>BABG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fit_width_landscape</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BAPP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fit_width_landscape</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BABI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fit_width_landscape</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>*</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>fit_single_page</t>
         </is>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -5681,7 +5681,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NoDecimal</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NoDecimal</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NoDecimal</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NoDecimal</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6017,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>NoDecimal</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>NoDecimal</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -7684,7 +7684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7802,10 +7802,82 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>WHOBG</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fit_width_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WHOPP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fit_width_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WHBBG</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fit_width_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WHBPP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fit_width_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WHPBG</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fit_width_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WHPPP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fit_width_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>*</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>fit_single_page</t>
         </is>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -3795,7 +3795,7 @@
         <v>2</v>
       </c>
       <c r="D113" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="114">
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="115">
@@ -3845,7 +3845,7 @@
         <v>2</v>
       </c>
       <c r="D116" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="117">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="118">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="121">
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="124">
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="141">
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="143">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NoDecimal</t>
+          <t>#,##0</t>
         </is>
       </c>
     </row>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NoDecimal</t>
+          <t>#,##0</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NoDecimal</t>
+          <t>#,##0</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>NoDecimal</t>
+          <t>#,##0</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NoDecimal</t>
+          <t>#,##0</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>NoDecimal</t>
+          <t>#,##0</t>
         </is>
       </c>
     </row>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -7684,7 +7684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7874,10 +7874,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>TRDEF</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fit_single_page</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>fit_width_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>*</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>fit_single_page</t>
         </is>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -7879,7 +7879,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>fit_single_page</t>
+          <t>fit_width_landscape</t>
         </is>
       </c>
     </row>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -6420,7 +6420,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>NoDecimal</t>
+          <t>#,##0</t>
         </is>
       </c>
     </row>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>$#,##0.000</t>
+          <t>$#,##0.00</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>$#,##0.000</t>
+          <t>$#,##0.00</t>
         </is>
       </c>
     </row>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -6588,7 +6588,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>NoDecimal</t>
+          <t>#,##0</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>$#,##0</t>
         </is>
       </c>
     </row>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -6378,7 +6378,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>$#,##0.000</t>
+          <t>$#,##0.00</t>
         </is>
       </c>
     </row>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>NoDecimal</t>
+          <t>#,##0</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NoDecimal</t>
+          <t>#,##0</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>$#,##0.000</t>
+          <t>$#,##0.00</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>NoDecimal</t>
+          <t>#,##0</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>$#,##0.000</t>
+          <t>$#,##0.00</t>
         </is>
       </c>
     </row>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D220"/>
+  <dimension ref="A1:D222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5572,6 +5572,38 @@
       </c>
       <c r="D220" t="n">
         <v>105</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>PDLD_HAB</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>1</v>
+      </c>
+      <c r="C221" t="n">
+        <v>1</v>
+      </c>
+      <c r="D221" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>PDLD_HAB</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>2</v>
+      </c>
+      <c r="C222" t="n">
+        <v>2</v>
+      </c>
+      <c r="D222" t="n">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -5585,7 +5617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6860,6 +6892,27 @@
         <v>4</v>
       </c>
       <c r="E60" t="inlineStr">
+        <is>
+          <t>$#,##0</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PDLD_HAB</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>4</v>
+      </c>
+      <c r="E61" t="inlineStr">
         <is>
           <t>$#,##0</t>
         </is>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D222"/>
+  <dimension ref="A1:D242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5604,6 +5604,332 @@
       </c>
       <c r="D222" t="n">
         <v>54</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>2</v>
+      </c>
+      <c r="C223" t="n">
+        <v>2</v>
+      </c>
+      <c r="D223" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>3</v>
+      </c>
+      <c r="C224" t="n">
+        <v>3</v>
+      </c>
+      <c r="D224" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>DCEQ</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>1</v>
+      </c>
+      <c r="C225" t="n">
+        <v>1</v>
+      </c>
+      <c r="D225" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>1</v>
+      </c>
+      <c r="C226" t="n">
+        <v>1</v>
+      </c>
+      <c r="D226" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>2</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>1</v>
+      </c>
+      <c r="C228" t="n">
+        <v>1</v>
+      </c>
+      <c r="D228" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>2</v>
+      </c>
+      <c r="C229" t="n">
+        <v>2</v>
+      </c>
+      <c r="D229" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>3</v>
+      </c>
+      <c r="C230" t="n">
+        <v>3</v>
+      </c>
+      <c r="D230" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>2</v>
+      </c>
+      <c r="C231" t="n">
+        <v>2</v>
+      </c>
+      <c r="D231" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>HE</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>1</v>
+      </c>
+      <c r="C232" t="n">
+        <v>1</v>
+      </c>
+      <c r="D232" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>HE</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>2</v>
+      </c>
+      <c r="C233" t="n">
+        <v>2</v>
+      </c>
+      <c r="D233" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>OPTI</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>1</v>
+      </c>
+      <c r="C234" t="n">
+        <v>1</v>
+      </c>
+      <c r="D234" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>OPTI</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>2</v>
+      </c>
+      <c r="C235" t="n">
+        <v>2</v>
+      </c>
+      <c r="D235" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>PED</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>1</v>
+      </c>
+      <c r="C236" t="n">
+        <v>1</v>
+      </c>
+      <c r="D236" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>PED</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>2</v>
+      </c>
+      <c r="C237" t="n">
+        <v>2</v>
+      </c>
+      <c r="D237" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>RTS</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>1</v>
+      </c>
+      <c r="C238" t="n">
+        <v>1</v>
+      </c>
+      <c r="D238" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>LS_RETAIL</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>1</v>
+      </c>
+      <c r="C239" t="n">
+        <v>2</v>
+      </c>
+      <c r="D239" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>LS_RETAIL</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>3</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>LS_RETAIL_CURRENT</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>1</v>
+      </c>
+      <c r="C241" t="n">
+        <v>2</v>
+      </c>
+      <c r="D241" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>LS_RETAIL_CURRENT</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>3</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -5617,7 +5943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6918,6 +7244,174 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>#,##0</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>$#,##0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>HE</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" t="n">
+        <v>4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>$#,##0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>OPTI</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="n">
+        <v>4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>$#,##0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PED</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="n">
+        <v>4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>$#,##0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>RTS</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>$#,##0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>LS_RETAIL</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>#,##0</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>LS_RETAIL_CURRENT</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>#,##0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6929,7 +7423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7672,6 +8166,68 @@
           <t>Named Storm Deductible</t>
         </is>
       </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LS_RETAIL</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>A:B</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Building plus Business Personal Property</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>C:REST</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LS_RETAIL_CURRENT</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>A:B</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Building plus Business Personal Property</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>C:REST</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D242"/>
+  <dimension ref="A1:D249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5930,6 +5930,122 @@
       </c>
       <c r="D242" t="n">
         <v>125</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>FU</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>1</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>1</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>1</v>
+      </c>
+      <c r="C245" t="n">
+        <v>3</v>
+      </c>
+      <c r="D245" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>PSS</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>1</v>
+      </c>
+      <c r="C246" t="n">
+        <v>3</v>
+      </c>
+      <c r="D246" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>PSPL</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>1</v>
+      </c>
+      <c r="C247" t="n">
+        <v>1</v>
+      </c>
+      <c r="D247" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>PSPL</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>2</v>
+      </c>
+      <c r="C248" t="n">
+        <v>2</v>
+      </c>
+      <c r="D248" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>MPVS</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>1</v>
+      </c>
+      <c r="C249" t="n">
+        <v>2</v>
+      </c>
+      <c r="D249" t="n">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -5943,7 +6059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7409,6 +7525,50 @@
       <c r="E69" t="inlineStr">
         <is>
           <t>#,##0</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>FUMP</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>$#,##0</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>$#,##0.00</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8356,6 @@
           <t>C:REST</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8227,7 +8386,6 @@
           <t>C:REST</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D249"/>
+  <dimension ref="A1:D251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6046,6 +6046,38 @@
       </c>
       <c r="D249" t="n">
         <v>150</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>LPGE_RETAIL</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>1</v>
+      </c>
+      <c r="C250" t="n">
+        <v>1</v>
+      </c>
+      <c r="D250" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>LPGE_RETAIL</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>2</v>
+      </c>
+      <c r="C251" t="n">
+        <v>2</v>
+      </c>
+      <c r="D251" t="n">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -6059,7 +6091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7567,6 +7599,48 @@
         <v>4</v>
       </c>
       <c r="E71" t="inlineStr">
+        <is>
+          <t>$#,##0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>LPGE_RETAIL</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>#,##0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>LPGE_RETAIL</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="n">
+        <v>4</v>
+      </c>
+      <c r="E73" t="inlineStr">
         <is>
           <t>$#,##0.00</t>
         </is>

--- a/BOP/BOP Input File.xlsx
+++ b/BOP/BOP Input File.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D251"/>
+  <dimension ref="A1:D258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5947,7 +5947,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
     </row>
     <row r="244">
@@ -6078,6 +6078,128 @@
       </c>
       <c r="D251" t="n">
         <v>200</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>OPTO</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>1</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>VET</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>1</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>AES</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>1</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>VPL</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>1</v>
+      </c>
+      <c r="C255" t="n">
+        <v>1</v>
+      </c>
+      <c r="D255" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>VPL</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>2</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>PSPL_OFFICE</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>1</v>
+      </c>
+      <c r="C257" t="n">
+        <v>1</v>
+      </c>
+      <c r="D257" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>PSPL_OFFICE</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>2</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -6091,7 +6213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7641,6 +7763,52 @@
         <v>4</v>
       </c>
       <c r="E73" t="inlineStr">
+        <is>
+          <t>$#,##0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>OPTO</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>$#,##0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>VET</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>4</v>
+      </c>
+      <c r="E75" t="inlineStr">
         <is>
           <t>$#,##0.00</t>
         </is>
